--- a/exports/xlsx/terms_definition_3.xlsx
+++ b/exports/xlsx/terms_definition_3.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,37 +417,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>term</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>definition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>examples</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>

--- a/exports/xlsx/terms_definition_3.xlsx
+++ b/exports/xlsx/terms_definition_3.xlsx
@@ -456,63 +456,78 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Uncertainty</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>Instrument Data</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>- core
+description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Uncertainty is a measure of the spread of the distribution of possible values.</t>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Verification</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>Auxiliary Data</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Verification serves as a means to evaluate the reliability of the Data in the absence of a Reference dataset, allowing for an assessment of its standalone performance. It involves confirming the consistency and internal coherence of the Data without direct comparison to external Reference sources.</t>
+          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CEOS-ARD PFS template 20220302</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Uncertainty</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>- core
+description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument’s sensor data by virtue of services provided</t>
+          <t>Measure of the spread of the distribution of possible values.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
         </is>
       </c>
     </row>
@@ -522,16 +537,21 @@
           <t>Validation</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>- core
+description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. It often involves acceptance and suitability with external customers.</t>
+          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of Calibration Data in order to control their change over time.</t>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -544,21 +564,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Auxiliary Data</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>Verification</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>- core
+description: Provision of objective evidence that a given item fulfils specified requirements.</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The Data required for instrument processing, which does not originate in the instrument itself or from the satellite. Some auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
+          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
+          <t>- KCEO</t>
         </is>
       </c>
     </row>

--- a/exports/xlsx/terms_definition_3.xlsx
+++ b/exports/xlsx/terms_definition_3.xlsx
@@ -456,26 +456,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>- core
-description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+description: Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
     </row>
@@ -508,82 +508,82 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uncertainty</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>- core
-description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Measure of the spread of the distribution of possible values.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+          <t>- EU-US Land Imaging EO Collaboration</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Uncertainty</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>- core
-description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+          <t>Measure of the spread of the distribution of possible values.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Instrument Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>- core
-description: Provision of objective evidence that a given item fulfils specified requirements.</t>
+description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
     </row>

--- a/exports/xlsx/terms_definition_3.xlsx
+++ b/exports/xlsx/terms_definition_3.xlsx
@@ -456,26 +456,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Instrument Data</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>- core
-description: Provision of objective evidence that a given item fulfils specified requirements.</t>
+description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
     </row>
@@ -508,82 +508,82 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Uncertainty</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>- core
-description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+          <t>Measure of the spread of the distribution of possible values.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Uncertainty</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>- core
-description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Measure of the spread of the distribution of possible values.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+          <t>- EU-US Land Imaging EO Collaboration</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>- core
-description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+description: Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
     </row>

--- a/exports/xlsx/terms_definition_3.xlsx
+++ b/exports/xlsx/terms_definition_3.xlsx
@@ -462,6 +462,7 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
@@ -488,7 +489,7 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -514,6 +515,7 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
@@ -544,6 +546,7 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
@@ -570,6 +573,7 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>

--- a/exports/xlsx/terms_definition_3.xlsx
+++ b/exports/xlsx/terms_definition_3.xlsx
@@ -456,138 +456,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Instrument Data</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>- core
+  - to be approved
+description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Auxiliary Data</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Uncertainty</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Measure of the spread of the distribution of possible values.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>- EU-US Land Imaging EO Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Verification</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>- core
 - to be approved
 description: Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Auxiliary Data</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Uncertainty</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Measure of the spread of the distribution of possible values.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Instrument Data</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>- core
-  - to be approved
-description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
     </row>

--- a/exports/xlsx/terms_definition_3.xlsx
+++ b/exports/xlsx/terms_definition_3.xlsx
@@ -456,138 +456,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Verification</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+description: Provision of objective evidence that a given item fulfils specified requirements.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Auxiliary Data</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>- EU-US Land Imaging EO Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Uncertainty</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Measure of the spread of the distribution of possible values.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Instrument Data</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>- core
   - to be approved
 description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Auxiliary Data</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Uncertainty</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Measure of the spread of the distribution of possible values.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Verification</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-description: Provision of objective evidence that a given item fulfils specified requirements.</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
     </row>

--- a/exports/xlsx/terms_definition_3.xlsx
+++ b/exports/xlsx/terms_definition_3.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,27 +456,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Instrument Data</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Provision of objective evidence that a given item fulfils specified requirements.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+- calval ingest
+- WGCV
+- WGClimate</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sensor Data, Sensor Data Record</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
     </row>
@@ -489,7 +495,10 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+- calval ingest
+- WGCV
+- WGClimate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -509,85 +518,156 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Uncertainty</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+- calval ingest
+- WGCV
+- WGISS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+          <t>Measure of the spread of the distribution of possible values.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Uncertainty</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+- calval ingest
+- WGCV
+- WGClimate</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Measure of the spread of the distribution of possible values.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Assurance that a product, service, or system meets customer and stakeholder needs through acceptance and suitability evaluation.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+          <t>- EU-US Land Imaging EO Collaboration</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>- core
-  - to be approved
-description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+          <t>- base
+- to be approved
+- calval ingest
+- WGISS
+- WGCV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+          <t>Property of a phenomenon, body, or substance with a magnitude expressible as a number and a reference.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- CEOS CalVal Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Evaluation of data reliability in the absence of a reference dataset, confirming consistency and internal coherence.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ancillary Data</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGISS
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Data not from the sensor, provided in science telemetry, used to process instrument data and including spacecraft engineering, housekeeping, or subsystem parameters.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OASIS equivalent definition is ancillary data can be considered as a Digital Data Object (object composed of a set of bit sequences) part of a Content Information, related to other digital objects (i.e. Primary Data) through Context Information (the information that documents the relationships of the Content Information to its environment; this includes why the Content Information was created and how it relates to other Content Information objects) or as a compound digital object which contains a mixture of Provenance, Context and Representation Information related to a Primary Digital Data Object</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- [CEOS-WGISS Document: Auxiliary Data in the CEOS Community: Reference Guidelines Document Part 1: Current Usage (1996) accessible at wgiss.ceos.org/archive/archive.doc/ads200part1.doc](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DAncillary%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc)
+- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- NESDIS Data Management Lexicon and Related Terms</t>
         </is>
       </c>
     </row>

--- a/exports/xlsx/terms_definition_3.xlsx
+++ b/exports/xlsx/terms_definition_3.xlsx
@@ -456,10 +456,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
+          <t>Ancillary Data</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGISS
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Data not from the sensor, provided in science telemetry, used to process instrument data and including spacecraft engineering, housekeeping, or subsystem parameters.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OASIS equivalent definition is ancillary data can be considered as a Digital Data Object (object composed of a set of bit sequences) part of a Content Information, related to other digital objects (i.e. Primary Data) through Context Information (the information that documents the relationships of the Content Information to its environment; this includes why the Content Information was created and how it relates to other Content Information objects) or as a compound digital object which contains a mixture of Provenance, Context and Representation Information related to a Primary Digital Data Object</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- [CEOS-WGISS Document: Auxiliary Data in the CEOS Community: Reference Guidelines Document Part 1: Current Usage (1996) accessible at wgiss.ceos.org/archive/archive.doc/ads200part1.doc](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DAncillary%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc)
+- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- NESDIS Data Management Lexicon and Related Terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>- base
+- to be approved
+- calval ingest
+- WGISS
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Property of a phenomenon, body, or substance with a magnitude expressible as a number and a reference.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>- CEOS CalVal Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>- core
 - to be approved
@@ -468,31 +533,31 @@
 - WGClimate</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Sensor Data, Sensor Data Record</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Assurance that a product, service, or system meets customer and stakeholder needs through acceptance and suitability evaluation.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>- EU-US Land Imaging EO Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Auxiliary Data</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>- core
 - to be approved
@@ -501,27 +566,27 @@
 - WGClimate</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>- CEOS-ARD PFS template 20220302</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Uncertainty</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>- core
 - to be approved
@@ -530,27 +595,56 @@
 - WGISS</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Evaluation of data reliability in the absence of a reference dataset, confirming consistency and internal coherence.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Uncertainty</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Measure of the spread of the distribution of possible values.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Instrument Data</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>- core
 - to be approved
@@ -559,115 +653,21 @@
 - WGClimate</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Assurance that a product, service, or system meets customer and stakeholder needs through acceptance and suitability evaluation.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>- base
-- to be approved
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Property of a phenomenon, body, or substance with a magnitude expressible as a number and a reference.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>- CEOS CalVal Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Verification</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGISS</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Evaluation of data reliability in the absence of a reference dataset, confirming consistency and internal coherence.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Ancillary Data</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sensor Data, Sensor Data Record</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Data not from the sensor, provided in science telemetry, used to process instrument data and including spacecraft engineering, housekeeping, or subsystem parameters.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>OASIS equivalent definition is ancillary data can be considered as a Digital Data Object (object composed of a set of bit sequences) part of a Content Information, related to other digital objects (i.e. Primary Data) through Context Information (the information that documents the relationships of the Content Information to its environment; this includes why the Content Information was created and how it relates to other Content Information objects) or as a compound digital object which contains a mixture of Provenance, Context and Representation Information related to a Primary Digital Data Object</t>
-        </is>
-      </c>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- [CEOS-WGISS Document: Auxiliary Data in the CEOS Community: Reference Guidelines Document Part 1: Current Usage (1996) accessible at wgiss.ceos.org/archive/archive.doc/ads200part1.doc](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DAncillary%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc)
-- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- NESDIS Data Management Lexicon and Related Terms</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
     </row>

--- a/exports/xlsx/terms_definition_3.xlsx
+++ b/exports/xlsx/terms_definition_3.xlsx
@@ -492,10 +492,163 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Verification</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Evaluation of data reliability in the absence of a reference dataset, confirming consistency and internal coherence.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGClimate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Assurance that a product, service, or system meets customer and stakeholder needs through acceptance and suitability evaluation.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>- EU-US Land Imaging EO Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Uncertainty</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Measure of the spread of the distribution of possible values.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Instrument Data</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGClimate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sensor Data, Sensor Data Record</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Auxiliary Data</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGClimate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>- base
 - to be approved
@@ -504,170 +657,17 @@
 - WGCV</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Property of a phenomenon, body, or substance with a magnitude expressible as a number and a reference.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>- CEOS CalVal Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGClimate</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Assurance that a product, service, or system meets customer and stakeholder needs through acceptance and suitability evaluation.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Auxiliary Data</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGClimate</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Verification</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGISS</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Evaluation of data reliability in the absence of a reference dataset, confirming consistency and internal coherence.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Uncertainty</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGISS</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Measure of the spread of the distribution of possible values.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Instrument Data</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGClimate</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sensor Data, Sensor Data Record</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- CEOS CalVal Portal</t>
         </is>
       </c>
     </row>
